--- a/ZonasEscolares/excels/JUNIN-HUANCAYO-CHILCA.xlsx
+++ b/ZonasEscolares/excels/JUNIN-HUANCAYO-CHILCA.xlsx
@@ -486,7 +486,7 @@
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>mantenimiento</t>
+          <t>Intervenido PI2024</t>
         </is>
       </c>
     </row>
@@ -538,7 +538,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -590,7 +590,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -642,7 +642,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -694,7 +694,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -746,7 +746,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -798,7 +798,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -902,7 +902,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -954,7 +954,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1006,7 +1006,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -1058,7 +1058,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1110,7 +1110,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1162,7 +1162,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -1214,7 +1214,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -1266,7 +1266,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1318,7 +1318,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1370,7 +1370,7 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -1422,7 +1422,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1474,7 +1474,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1526,7 +1526,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -1578,7 +1578,7 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1630,7 +1630,7 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -1682,7 +1682,7 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -1734,7 +1734,7 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -1786,7 +1786,7 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>

--- a/ZonasEscolares/excels/JUNIN-HUANCAYO-CHILCA.xlsx
+++ b/ZonasEscolares/excels/JUNIN-HUANCAYO-CHILCA.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -429,62 +417,62 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>ubigeo_gestor</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>departamento</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>provincia</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>distrito</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>codigo_ce</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>descripcion</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>latitud</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>longitud</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>alumnos</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>docentes</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>siniestros</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>Intervenido PI2024</t>
         </is>
@@ -521,20 +509,30 @@
           <t>430</t>
         </is>
       </c>
-      <c r="G2" t="n">
-        <v>-12.095</v>
-      </c>
-      <c r="H2" t="n">
-        <v>-75.1915</v>
-      </c>
-      <c r="I2" t="n">
-        <v>237</v>
-      </c>
-      <c r="J2" t="n">
-        <v>9</v>
-      </c>
-      <c r="K2" t="n">
-        <v>0</v>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>-12.095</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>-75.1915</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>237</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
@@ -573,20 +571,30 @@
           <t>435 JOSE GALVES</t>
         </is>
       </c>
-      <c r="G3" t="n">
-        <v>-12.08726</v>
-      </c>
-      <c r="H3" t="n">
-        <v>-75.20583999999999</v>
-      </c>
-      <c r="I3" t="n">
-        <v>225</v>
-      </c>
-      <c r="J3" t="n">
-        <v>10</v>
-      </c>
-      <c r="K3" t="n">
-        <v>0</v>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>-12.08726</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>-75.20584</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>225</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
@@ -625,20 +633,30 @@
           <t>30012 VICTOR ALBERTO GIL MALLMA</t>
         </is>
       </c>
-      <c r="G4" t="n">
-        <v>-12.07839</v>
-      </c>
-      <c r="H4" t="n">
-        <v>-75.19661000000001</v>
-      </c>
-      <c r="I4" t="n">
-        <v>969</v>
-      </c>
-      <c r="J4" t="n">
-        <v>54</v>
-      </c>
-      <c r="K4" t="n">
-        <v>0</v>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>-12.07839</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>-75.19661</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>969</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
@@ -677,20 +695,30 @@
           <t>30152 LA MEDALLA MILAGROSA</t>
         </is>
       </c>
-      <c r="G5" t="n">
-        <v>-12.08745</v>
-      </c>
-      <c r="H5" t="n">
-        <v>-75.21979</v>
-      </c>
-      <c r="I5" t="n">
-        <v>312</v>
-      </c>
-      <c r="J5" t="n">
-        <v>15</v>
-      </c>
-      <c r="K5" t="n">
-        <v>0</v>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>-12.08745</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>-75.21979</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>312</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
@@ -729,20 +757,30 @@
           <t>30153 MARIA N. SALAZAR AGUILAR</t>
         </is>
       </c>
-      <c r="G6" t="n">
-        <v>-12.088048</v>
-      </c>
-      <c r="H6" t="n">
-        <v>-75.19954300000001</v>
-      </c>
-      <c r="I6" t="n">
-        <v>852</v>
-      </c>
-      <c r="J6" t="n">
-        <v>48</v>
-      </c>
-      <c r="K6" t="n">
-        <v>0</v>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>-12.088048</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>-75.199543</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>852</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
@@ -781,20 +819,30 @@
           <t>30154 INMACULADO CORAZON DE MARIA</t>
         </is>
       </c>
-      <c r="G7" t="n">
-        <v>-12.08095</v>
-      </c>
-      <c r="H7" t="n">
-        <v>-75.20560999999999</v>
-      </c>
-      <c r="I7" t="n">
-        <v>569</v>
-      </c>
-      <c r="J7" t="n">
-        <v>31</v>
-      </c>
-      <c r="K7" t="n">
-        <v>0</v>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>-12.08095</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>-75.20561</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>569</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
@@ -833,20 +881,30 @@
           <t>30155 FRANCISCO BOLOGNESI</t>
         </is>
       </c>
-      <c r="G8" t="n">
-        <v>-12.08608</v>
-      </c>
-      <c r="H8" t="n">
-        <v>-75.21057999999999</v>
-      </c>
-      <c r="I8" t="n">
-        <v>676</v>
-      </c>
-      <c r="J8" t="n">
-        <v>33</v>
-      </c>
-      <c r="K8" t="n">
-        <v>0</v>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>-12.08608</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>-75.21058</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>676</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
@@ -885,20 +943,30 @@
           <t>30170</t>
         </is>
       </c>
-      <c r="G9" t="n">
-        <v>-12.09816</v>
-      </c>
-      <c r="H9" t="n">
-        <v>-75.2118</v>
-      </c>
-      <c r="I9" t="n">
-        <v>239</v>
-      </c>
-      <c r="J9" t="n">
-        <v>12</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0</v>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>-12.09816</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>-75.2118</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>239</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
@@ -937,20 +1005,30 @@
           <t>31301 JOSE GALVEZ EGUSQUIZA</t>
         </is>
       </c>
-      <c r="G10" t="n">
-        <v>-12.0869</v>
-      </c>
-      <c r="H10" t="n">
-        <v>-75.20440000000001</v>
-      </c>
-      <c r="I10" t="n">
-        <v>561</v>
-      </c>
-      <c r="J10" t="n">
-        <v>23</v>
-      </c>
-      <c r="K10" t="n">
-        <v>0</v>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>-12.0869</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>-75.2044</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>561</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
@@ -989,20 +1067,30 @@
           <t>31543 TUPAC AMARU</t>
         </is>
       </c>
-      <c r="G11" t="n">
-        <v>-12.0962548958917</v>
-      </c>
-      <c r="H11" t="n">
-        <v>-75.1913272190753</v>
-      </c>
-      <c r="I11" t="n">
-        <v>885</v>
-      </c>
-      <c r="J11" t="n">
-        <v>39</v>
-      </c>
-      <c r="K11" t="n">
-        <v>0</v>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>-12.0962548958917</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>-75.1913272190753</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>885</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
@@ -1041,20 +1129,30 @@
           <t>POLITECNICO TUPAC AMARU</t>
         </is>
       </c>
-      <c r="G12" t="n">
-        <v>-12.09624</v>
-      </c>
-      <c r="H12" t="n">
-        <v>-75.19256</v>
-      </c>
-      <c r="I12" t="n">
-        <v>1694</v>
-      </c>
-      <c r="J12" t="n">
-        <v>103</v>
-      </c>
-      <c r="K12" t="n">
-        <v>0</v>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>-12.09624</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>-75.19256</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1694</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>103</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
@@ -1093,20 +1191,30 @@
           <t>SANTA BARBARA</t>
         </is>
       </c>
-      <c r="G13" t="n">
-        <v>-12.086587</v>
-      </c>
-      <c r="H13" t="n">
-        <v>-75.204739</v>
-      </c>
-      <c r="I13" t="n">
-        <v>331</v>
-      </c>
-      <c r="J13" t="n">
-        <v>20</v>
-      </c>
-      <c r="K13" t="n">
-        <v>0</v>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>-12.086587</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>-75.204739</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>331</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
@@ -1145,20 +1253,30 @@
           <t>BERNARD BLENKIR</t>
         </is>
       </c>
-      <c r="G14" t="n">
-        <v>-12.09042</v>
-      </c>
-      <c r="H14" t="n">
-        <v>-75.20526</v>
-      </c>
-      <c r="I14" t="n">
-        <v>534</v>
-      </c>
-      <c r="J14" t="n">
-        <v>13</v>
-      </c>
-      <c r="K14" t="n">
-        <v>0</v>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>-12.09042</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>-75.20526</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>534</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
@@ -1197,20 +1315,30 @@
           <t>WINNER</t>
         </is>
       </c>
-      <c r="G15" t="n">
-        <v>-12.08627</v>
-      </c>
-      <c r="H15" t="n">
-        <v>-75.20153999999999</v>
-      </c>
-      <c r="I15" t="n">
-        <v>155</v>
-      </c>
-      <c r="J15" t="n">
-        <v>17</v>
-      </c>
-      <c r="K15" t="n">
-        <v>0</v>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>-12.08627</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>-75.20154</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>155</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
@@ -1249,20 +1377,30 @@
           <t>NUEVA ANTIOQUIA</t>
         </is>
       </c>
-      <c r="G16" t="n">
-        <v>-12.09139</v>
-      </c>
-      <c r="H16" t="n">
-        <v>-75.19925000000001</v>
-      </c>
-      <c r="I16" t="n">
-        <v>530</v>
-      </c>
-      <c r="J16" t="n">
-        <v>14</v>
-      </c>
-      <c r="K16" t="n">
-        <v>0</v>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>-12.09139</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>-75.19925</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>530</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
@@ -1301,20 +1439,30 @@
           <t>UNION PACIFICO</t>
         </is>
       </c>
-      <c r="G17" t="n">
-        <v>-12.08773</v>
-      </c>
-      <c r="H17" t="n">
-        <v>-75.19931</v>
-      </c>
-      <c r="I17" t="n">
-        <v>247</v>
-      </c>
-      <c r="J17" t="n">
-        <v>18</v>
-      </c>
-      <c r="K17" t="n">
-        <v>0</v>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>-12.08773</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>-75.19931</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>247</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
@@ -1353,20 +1501,30 @@
           <t>ANGELITOS</t>
         </is>
       </c>
-      <c r="G18" t="n">
-        <v>-12.08368</v>
-      </c>
-      <c r="H18" t="n">
-        <v>-75.20295</v>
-      </c>
-      <c r="I18" t="n">
-        <v>15</v>
-      </c>
-      <c r="J18" t="n">
-        <v>4</v>
-      </c>
-      <c r="K18" t="n">
-        <v>0</v>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>-12.08368</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>-75.20295</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
@@ -1405,20 +1563,30 @@
           <t>NUESTRA SEÑORA DE LAS MERCEDES</t>
         </is>
       </c>
-      <c r="G19" t="n">
-        <v>-12.08122</v>
-      </c>
-      <c r="H19" t="n">
-        <v>-75.20227</v>
-      </c>
-      <c r="I19" t="n">
-        <v>279</v>
-      </c>
-      <c r="J19" t="n">
-        <v>30</v>
-      </c>
-      <c r="K19" t="n">
-        <v>0</v>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>-12.08122</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>-75.20227</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>279</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
@@ -1457,20 +1625,30 @@
           <t>BERNARD BLENKIR</t>
         </is>
       </c>
-      <c r="G20" t="n">
-        <v>-12.08858</v>
-      </c>
-      <c r="H20" t="n">
-        <v>-75.20347</v>
-      </c>
-      <c r="I20" t="n">
-        <v>233</v>
-      </c>
-      <c r="J20" t="n">
-        <v>10</v>
-      </c>
-      <c r="K20" t="n">
-        <v>0</v>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>-12.08858</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>-75.20347</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>233</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
@@ -1509,20 +1687,30 @@
           <t>MOODY</t>
         </is>
       </c>
-      <c r="G21" t="n">
-        <v>-12.081641</v>
-      </c>
-      <c r="H21" t="n">
-        <v>-75.199522</v>
-      </c>
-      <c r="I21" t="n">
-        <v>550</v>
-      </c>
-      <c r="J21" t="n">
-        <v>29</v>
-      </c>
-      <c r="K21" t="n">
-        <v>0</v>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>-12.081641</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>-75.199522</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>550</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
@@ -1561,20 +1749,30 @@
           <t>1112</t>
         </is>
       </c>
-      <c r="G22" t="n">
-        <v>-12.08132</v>
-      </c>
-      <c r="H22" t="n">
-        <v>-75.18937</v>
-      </c>
-      <c r="I22" t="n">
-        <v>48</v>
-      </c>
-      <c r="J22" t="n">
-        <v>2</v>
-      </c>
-      <c r="K22" t="n">
-        <v>1</v>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>-12.08132</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>-75.18937</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
@@ -1613,20 +1811,30 @@
           <t>ORION INTERNACIONAL</t>
         </is>
       </c>
-      <c r="G23" t="n">
-        <v>-12.082508</v>
-      </c>
-      <c r="H23" t="n">
-        <v>-75.20286299999999</v>
-      </c>
-      <c r="I23" t="n">
-        <v>392</v>
-      </c>
-      <c r="J23" t="n">
-        <v>31</v>
-      </c>
-      <c r="K23" t="n">
-        <v>0</v>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>-12.082508</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>-75.202863</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>392</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
@@ -1665,20 +1873,30 @@
           <t>UNION INTERNACIONAL</t>
         </is>
       </c>
-      <c r="G24" t="n">
-        <v>-12.07737</v>
-      </c>
-      <c r="H24" t="n">
-        <v>-75.197005</v>
-      </c>
-      <c r="I24" t="n">
-        <v>353</v>
-      </c>
-      <c r="J24" t="n">
-        <v>20</v>
-      </c>
-      <c r="K24" t="n">
-        <v>0</v>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>-12.07737</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>-75.197005</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>353</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
@@ -1717,20 +1935,30 @@
           <t>BLENKIR AUQUIMARCA</t>
         </is>
       </c>
-      <c r="G25" t="n">
-        <v>-12.084903</v>
-      </c>
-      <c r="H25" t="n">
-        <v>-75.21595499999999</v>
-      </c>
-      <c r="I25" t="n">
-        <v>187</v>
-      </c>
-      <c r="J25" t="n">
-        <v>11</v>
-      </c>
-      <c r="K25" t="n">
-        <v>0</v>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>-12.084903</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>-75.215955</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>187</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
@@ -1769,20 +1997,30 @@
           <t>JOSE MARIA ARGUEDAS</t>
         </is>
       </c>
-      <c r="G26" t="n">
-        <v>-12.09348</v>
-      </c>
-      <c r="H26" t="n">
-        <v>-75.21787</v>
-      </c>
-      <c r="I26" t="n">
-        <v>299</v>
-      </c>
-      <c r="J26" t="n">
-        <v>32</v>
-      </c>
-      <c r="K26" t="n">
-        <v>0</v>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>-12.09348</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>-75.21787</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>299</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>

--- a/ZonasEscolares/excels/JUNIN-HUANCAYO-CHILCA.xlsx
+++ b/ZonasEscolares/excels/JUNIN-HUANCAYO-CHILCA.xlsx
@@ -501,32 +501,32 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>221860</t>
+          <t>221879</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>430</t>
+          <t>435 JOSE GALVES</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>-12.095</t>
+          <t>-12.08726</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>-75.1915</t>
+          <t>-75.20584</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>237</t>
+          <t>225</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>10</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -563,27 +563,27 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>221879</t>
+          <t>646665</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>435 JOSE GALVES</t>
+          <t>BERNARD BLENKIR</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>-12.08726</t>
+          <t>-12.08858</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-75.20584</t>
+          <t>-75.20347</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>225</t>
+          <t>233</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -625,32 +625,32 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>221902</t>
+          <t>222001</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>30012 VICTOR ALBERTO GIL MALLMA</t>
+          <t>POLITECNICO TUPAC AMARU</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>-12.07839</t>
+          <t>-12.09624</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-75.19661</t>
+          <t>-75.19256</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>969</t>
+          <t>1694</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>103</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -660,7 +660,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -687,32 +687,32 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>221921</t>
+          <t>846240</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>30152 LA MEDALLA MILAGROSA</t>
+          <t>BLENKIR AUQUIMARCA</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>-12.08745</t>
+          <t>-12.084903</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-75.21979</t>
+          <t>-75.215955</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>312</t>
+          <t>187</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>11</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -722,7 +722,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -749,32 +749,32 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>221935</t>
+          <t>221964</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>30153 MARIA N. SALAZAR AGUILAR</t>
+          <t>30170</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>-12.088048</t>
+          <t>-12.09816</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-75.199543</t>
+          <t>-75.2118</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>852</t>
+          <t>239</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>12</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -784,7 +784,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -811,32 +811,32 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>221940</t>
+          <t>512736</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>30154 INMACULADO CORAZON DE MARIA</t>
+          <t>BERNARD BLENKIR</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>-12.08095</t>
+          <t>-12.09042</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-75.20561</t>
+          <t>-75.20526</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>569</t>
+          <t>534</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>13</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>221959</t>
+          <t>586322</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>30155 FRANCISCO BOLOGNESI</t>
+          <t>NUEVA ANTIOQUIA</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>-12.08608</t>
+          <t>-12.09139</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-75.21058</t>
+          <t>-75.19925</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>676</t>
+          <t>530</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>14</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -908,7 +908,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -935,32 +935,32 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>221964</t>
+          <t>221921</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>30170</t>
+          <t>30152 LA MEDALLA MILAGROSA</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>-12.09816</t>
+          <t>-12.08745</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-75.2118</t>
+          <t>-75.21979</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>239</t>
+          <t>312</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>15</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -997,32 +997,32 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>221978</t>
+          <t>585704</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>31301 JOSE GALVEZ EGUSQUIZA</t>
+          <t>WINNER</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>-12.0869</t>
+          <t>-12.08627</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-75.2044</t>
+          <t>-75.20154</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>561</t>
+          <t>155</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>17</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -1032,7 +1032,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -1059,32 +1059,32 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>221983</t>
+          <t>619803</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>31543 TUPAC AMARU</t>
+          <t>UNION PACIFICO</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>-12.0962548958917</t>
+          <t>-12.08773</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-75.1913272190753</t>
+          <t>-75.19931</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>885</t>
+          <t>247</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>18</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -1094,7 +1094,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1121,37 +1121,37 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>222001</t>
+          <t>729953</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>POLITECNICO TUPAC AMARU</t>
+          <t>1112</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>-12.09624</t>
+          <t>-12.08132</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-75.19256</t>
+          <t>-75.18937</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>1694</t>
+          <t>48</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>103</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
@@ -1245,32 +1245,32 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>512736</t>
+          <t>825426</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>BERNARD BLENKIR</t>
+          <t>UNION INTERNACIONAL</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>-12.09042</t>
+          <t>-12.07737</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>-75.20526</t>
+          <t>-75.197005</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>534</t>
+          <t>353</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>20</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -1307,32 +1307,32 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>585704</t>
+          <t>221978</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>WINNER</t>
+          <t>31301 JOSE GALVEZ EGUSQUIZA</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>-12.08627</t>
+          <t>-12.0869</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>-75.20154</t>
+          <t>-75.2044</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>155</t>
+          <t>561</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>23</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -1342,7 +1342,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1369,32 +1369,32 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>586322</t>
+          <t>685001</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>NUEVA ANTIOQUIA</t>
+          <t>MOODY</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>-12.09139</t>
+          <t>-12.081641</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>-75.19925</t>
+          <t>-75.199522</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>530</t>
+          <t>550</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>29</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -1431,32 +1431,32 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>619803</t>
+          <t>645562</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>UNION PACIFICO</t>
+          <t>NUESTRA SEÑORA DE LAS MERCEDES</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>-12.08773</t>
+          <t>-12.08122</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>-75.19931</t>
+          <t>-75.20227</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>247</t>
+          <t>279</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>30</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -1493,32 +1493,32 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>641899</t>
+          <t>221940</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>ANGELITOS</t>
+          <t>30154 INMACULADO CORAZON DE MARIA</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>-12.08368</t>
+          <t>-12.08095</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>-75.20295</t>
+          <t>-75.20561</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>569</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>31</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -1555,32 +1555,32 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>645562</t>
+          <t>748503</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>NUESTRA SEÑORA DE LAS MERCEDES</t>
+          <t>ORION INTERNACIONAL</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>-12.08122</t>
+          <t>-12.082508</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>-75.20227</t>
+          <t>-75.202863</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>279</t>
+          <t>392</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>31</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -1590,7 +1590,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -1617,32 +1617,32 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>646665</t>
+          <t>848814</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>BERNARD BLENKIR</t>
+          <t>JOSE MARIA ARGUEDAS</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>-12.08858</t>
+          <t>-12.09348</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>-75.20347</t>
+          <t>-75.21787</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>233</t>
+          <t>299</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>32</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -1679,32 +1679,32 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>685001</t>
+          <t>221959</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>MOODY</t>
+          <t>30155 FRANCISCO BOLOGNESI</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>-12.081641</t>
+          <t>-12.08608</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>-75.199522</t>
+          <t>-75.21058</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>550</t>
+          <t>676</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>33</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -1741,42 +1741,42 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>729953</t>
+          <t>221983</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>1112</t>
+          <t>31543 TUPAC AMARU</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>-12.08132</t>
+          <t>-12.0962548958917</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>-75.18937</t>
+          <t>-75.1913272190753</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>885</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>39</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -1803,32 +1803,32 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>748503</t>
+          <t>641899</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>ORION INTERNACIONAL</t>
+          <t>ANGELITOS</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>-12.082508</t>
+          <t>-12.08368</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>-75.202863</t>
+          <t>-75.20295</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>392</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>4</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -1865,32 +1865,32 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>825426</t>
+          <t>221935</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>UNION INTERNACIONAL</t>
+          <t>30153 MARIA N. SALAZAR AGUILAR</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>-12.07737</t>
+          <t>-12.088048</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>-75.197005</t>
+          <t>-75.199543</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>353</t>
+          <t>852</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>48</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
@@ -1927,32 +1927,32 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>846240</t>
+          <t>221902</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>BLENKIR AUQUIMARCA</t>
+          <t>30012 VICTOR ALBERTO GIL MALLMA</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>-12.084903</t>
+          <t>-12.07839</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>-75.215955</t>
+          <t>-75.19661</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>187</t>
+          <t>969</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>54</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
@@ -1989,32 +1989,32 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>848814</t>
+          <t>221860</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>JOSE MARIA ARGUEDAS</t>
+          <t>430</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>-12.09348</t>
+          <t>-12.095</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>-75.21787</t>
+          <t>-75.1915</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>299</t>
+          <t>237</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>9</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">

--- a/ZonasEscolares/excels/JUNIN-HUANCAYO-CHILCA.xlsx
+++ b/ZonasEscolares/excels/JUNIN-HUANCAYO-CHILCA.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L39"/>
+  <dimension ref="A1:L37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -501,32 +501,32 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>221879</t>
+          <t>907182</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>435 JOSE GALVES</t>
+          <t>MARYAM SCHOOL</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>-12.08726</t>
+          <t>27</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>-75.20584</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>225</t>
+          <t>-12.08014</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>-75.20392</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -563,32 +563,32 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>646665</t>
+          <t>848814</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>BERNARD BLENKIR</t>
+          <t>JOSE MARIA ARGUEDAS</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>-12.08858</t>
+          <t>299</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-75.20347</t>
+          <t>32</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>233</t>
+          <t>-12.09348</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>-75.21787</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -625,32 +625,32 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>222001</t>
+          <t>846240</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>POLITECNICO TUPAC AMARU</t>
+          <t>BLENKIR AUQUIMARCA</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>-12.09624</t>
+          <t>187</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-75.19256</t>
+          <t>11</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1694</t>
+          <t>-12.084903</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>103</t>
+          <t>-75.215955</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -660,7 +660,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -687,32 +687,32 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>846240</t>
+          <t>825426</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>BLENKIR AUQUIMARCA</t>
+          <t>UNION INTERNACIONAL</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>-12.084903</t>
+          <t>353</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-75.215955</t>
+          <t>20</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>187</t>
+          <t>-12.07737</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>-75.197005</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -749,32 +749,32 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>221964</t>
+          <t>814687</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>30170</t>
+          <t>NUEVA JERUSALEN</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>-12.09816</t>
+          <t>9</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-75.2118</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>239</t>
+          <t>-12.0772</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>-75.18461</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>512736</t>
+          <t>812315</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>BERNARD BLENKIR</t>
+          <t>SHEKINAH</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>-12.09042</t>
+          <t>36</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-75.20526</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>534</t>
+          <t>-12.08429</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>-75.19833</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -846,7 +846,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -873,32 +873,32 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>586322</t>
+          <t>748503</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>NUEVA ANTIOQUIA</t>
+          <t>ORION INTERNACIONAL</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>-12.09139</t>
+          <t>392</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-75.19925</t>
+          <t>31</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>530</t>
+          <t>-12.082508</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>-75.202863</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -908,7 +908,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -935,32 +935,32 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>221921</t>
+          <t>743336</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>30152 LA MEDALLA MILAGROSA</t>
+          <t>NASA S.A.</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>-12.08745</t>
+          <t>31</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-75.21979</t>
+          <t>13</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>312</t>
+          <t>-12.08577</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>-75.19885</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -997,32 +997,32 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>585704</t>
+          <t>743143</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>WINNER</t>
+          <t>PREMIUM</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>-12.08627</t>
+          <t>18</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-75.20154</t>
+          <t>10</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>155</t>
+          <t>-12.08234</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>-75.20471</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -1032,7 +1032,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1059,37 +1059,37 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>619803</t>
+          <t>729953</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>UNION PACIFICO</t>
+          <t>1112</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>-12.08773</t>
+          <t>48</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-75.19931</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>247</t>
+          <t>-12.08132</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>-75.18937</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -1121,42 +1121,42 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>729953</t>
+          <t>685001</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>1112</t>
+          <t>MOODY</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>-12.08132</t>
+          <t>550</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-75.18937</t>
+          <t>29</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>-12.081641</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>-75.199522</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -1183,32 +1183,32 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>222119</t>
+          <t>646665</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>SANTA BARBARA</t>
+          <t>BERNARD BLENKIR</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>-12.086587</t>
+          <t>233</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>-75.204739</t>
+          <t>10</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>331</t>
+          <t>-12.08858</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>-75.20347</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -1245,32 +1245,32 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>825426</t>
+          <t>645562</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>UNION INTERNACIONAL</t>
+          <t>NUESTRA SEÑORA DE LAS MERCEDES</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>-12.07737</t>
+          <t>279</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>-75.197005</t>
+          <t>30</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>353</t>
+          <t>-12.08122</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>-75.20227</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -1280,7 +1280,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1307,32 +1307,32 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>221978</t>
+          <t>642605</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>31301 JOSE GALVEZ EGUSQUIZA</t>
+          <t>SANTA MARIA DE GUADALUPE</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>-12.0869</t>
+          <t>21</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>-75.2044</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>561</t>
+          <t>-12.08788</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>-75.19563</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -1369,32 +1369,32 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>685001</t>
+          <t>642021</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>MOODY</t>
+          <t>LA CANTUTA MILENIUM III</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>-12.081641</t>
+          <t>57</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>-75.199522</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>550</t>
+          <t>-12.086012</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>-75.198187</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1431,32 +1431,32 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>645562</t>
+          <t>641899</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>NUESTRA SEÑORA DE LAS MERCEDES</t>
+          <t>ANGELITOS</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>-12.08122</t>
+          <t>15</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>-75.20227</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>279</t>
+          <t>-12.08368</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>-75.20295</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -1493,32 +1493,32 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>221940</t>
+          <t>641776</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>30154 INMACULADO CORAZON DE MARIA</t>
+          <t>PALMAS DEL EXITO</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>-12.08095</t>
+          <t>101</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>-75.20561</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>569</t>
+          <t>-12.08511</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>-75.22009</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1555,32 +1555,32 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>748503</t>
+          <t>619803</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>ORION INTERNACIONAL</t>
+          <t>UNION PACIFICO</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>-12.082508</t>
+          <t>247</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>-75.202863</t>
+          <t>18</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>392</t>
+          <t>-12.08773</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>-75.19931</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -1590,7 +1590,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1617,32 +1617,32 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>848814</t>
+          <t>586322</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>JOSE MARIA ARGUEDAS</t>
+          <t>NUEVA ANTIOQUIA</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>-12.09348</t>
+          <t>530</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>-75.21787</t>
+          <t>14</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>299</t>
+          <t>-12.09139</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>-75.19925</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -1679,32 +1679,32 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>221959</t>
+          <t>585704</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>30155 FRANCISCO BOLOGNESI</t>
+          <t>WINNER</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>-12.08608</t>
+          <t>155</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>-75.21058</t>
+          <t>17</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>676</t>
+          <t>-12.08627</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>-75.20154</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -1741,32 +1741,32 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>221983</t>
+          <t>512736</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>31543 TUPAC AMARU</t>
+          <t>BERNARD BLENKIR</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>-12.0962548958917</t>
+          <t>534</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>-75.1913272190753</t>
+          <t>13</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>885</t>
+          <t>-12.09042</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>-75.20526</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -1803,32 +1803,32 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>641899</t>
+          <t>511973</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>ANGELITOS</t>
+          <t>UNICIENCIA</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>-12.08368</t>
+          <t>59</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>-75.20295</t>
+          <t>16</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>-12.07876</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>-75.20372</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -1838,7 +1838,7 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1865,32 +1865,32 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>221935</t>
+          <t>222119</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>30153 MARIA N. SALAZAR AGUILAR</t>
+          <t>SANTA BARBARA</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>-12.088048</t>
+          <t>331</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>-75.199543</t>
+          <t>20</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>852</t>
+          <t>-12.086587</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>-75.204739</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
@@ -1900,7 +1900,7 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1927,32 +1927,32 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>221902</t>
+          <t>222096</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>30012 VICTOR ALBERTO GIL MALLMA</t>
+          <t>SANTA MARIA MAZZARELLO</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>-12.07839</t>
+          <t>88</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>-75.19661</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>969</t>
+          <t>-12.08236</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>-75.20433</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
@@ -1962,7 +1962,7 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1989,32 +1989,32 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>221860</t>
+          <t>222077</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>430</t>
+          <t>CESAR VALLEJO</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>-12.095</t>
+          <t>133</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>-75.1915</t>
+          <t>14</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>237</t>
+          <t>-12.08566</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>-75.20931</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
@@ -2051,32 +2051,32 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>221879</t>
+          <t>222001</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>435 JOSE GALVES</t>
+          <t>POLITECNICO TUPAC AMARU</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>-12.08726</t>
+          <t>1694</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>-75.20584</t>
+          <t>103</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>225</t>
+          <t>-12.09624</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>-75.19256</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
@@ -2113,32 +2113,32 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>222077</t>
+          <t>221983</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>CESAR VALLEJO</t>
+          <t>31543 TUPAC AMARU</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>-12.08566</t>
+          <t>885</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>-75.20931</t>
+          <t>39</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>133</t>
+          <t>-12.0962548958917</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>-75.1913272190753</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
@@ -2148,7 +2148,7 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -2175,32 +2175,32 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>222096</t>
+          <t>221978</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>SANTA MARIA MAZZARELLO</t>
+          <t>31301 JOSE GALVEZ EGUSQUIZA</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>-12.08236</t>
+          <t>561</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>-75.20433</t>
+          <t>23</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>-12.0869</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>-75.2044</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
@@ -2237,32 +2237,32 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>511973</t>
+          <t>221964</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>UNICIENCIA</t>
+          <t>30170</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>-12.07876</t>
+          <t>239</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>-75.20372</t>
+          <t>12</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>59</t>
+          <t>-12.09816</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>-75.2118</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
@@ -2299,32 +2299,32 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>512736</t>
+          <t>221959</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>BERNARD BLENKIR</t>
+          <t>30155 FRANCISCO BOLOGNESI</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>-12.09042</t>
+          <t>676</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>-75.20526</t>
+          <t>33</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>534</t>
+          <t>-12.08608</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>-75.21058</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
@@ -2334,7 +2334,7 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -2361,32 +2361,32 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>641776</t>
+          <t>221940</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>PALMAS DEL EXITO</t>
+          <t>30154 INMACULADO CORAZON DE MARIA</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>-12.08511</t>
+          <t>569</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>-75.22009</t>
+          <t>31</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>101</t>
+          <t>-12.08095</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>-75.20561</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
@@ -2396,7 +2396,7 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -2423,32 +2423,32 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>642021</t>
+          <t>221935</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>LA CANTUTA MILENIUM III</t>
+          <t>30153 MARIA N. SALAZAR AGUILAR</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>-12.086012</t>
+          <t>852</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>-75.198187</t>
+          <t>48</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>57</t>
+          <t>-12.088048</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>-75.199543</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
@@ -2458,7 +2458,7 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -2485,32 +2485,32 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>642605</t>
+          <t>221921</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>SANTA MARIA DE GUADALUPE</t>
+          <t>30152 LA MEDALLA MILAGROSA</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>-12.08788</t>
+          <t>312</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>-75.19563</t>
+          <t>15</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>-12.08745</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>-75.21979</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
@@ -2547,32 +2547,32 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>743143</t>
+          <t>221902</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>PREMIUM</t>
+          <t>30012 VICTOR ALBERTO GIL MALLMA</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>-12.08234</t>
+          <t>969</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>-75.20471</t>
+          <t>54</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>-12.07839</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>-75.19661</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
@@ -2582,7 +2582,7 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -2609,32 +2609,32 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>743336</t>
+          <t>221879</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>NASA S.A.</t>
+          <t>435 JOSE GALVES</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>-12.08577</t>
+          <t>225</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>-75.19885</t>
+          <t>10</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>-12.08726</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>-75.20584</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
@@ -2671,32 +2671,32 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>812315</t>
+          <t>221860</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>SHEKINAH</t>
+          <t>430</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>-12.08429</t>
+          <t>237</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>-75.19833</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>-12.095</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>-75.1915</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
@@ -2705,130 +2705,6 @@
         </is>
       </c>
       <c r="L37" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>120107</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>JUNIN</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>HUANCAYO</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>CHILCA</t>
-        </is>
-      </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>814687</t>
-        </is>
-      </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>NUEVA JERUSALEN</t>
-        </is>
-      </c>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>-12.0772</t>
-        </is>
-      </c>
-      <c r="H38" t="inlineStr">
-        <is>
-          <t>-75.18461</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="J38" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K38" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L38" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>120107</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>JUNIN</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>HUANCAYO</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>CHILCA</t>
-        </is>
-      </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>907182</t>
-        </is>
-      </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>MARYAM SCHOOL</t>
-        </is>
-      </c>
-      <c r="G39" t="inlineStr">
-        <is>
-          <t>-12.08014</t>
-        </is>
-      </c>
-      <c r="H39" t="inlineStr">
-        <is>
-          <t>-75.20392</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K39" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L39" t="inlineStr">
         <is>
           <t>No</t>
         </is>

--- a/ZonasEscolares/excels/JUNIN-HUANCAYO-CHILCA.xlsx
+++ b/ZonasEscolares/excels/JUNIN-HUANCAYO-CHILCA.xlsx
@@ -449,22 +449,22 @@
       </c>
       <c r="G1" t="inlineStr">
         <is>
+          <t>alumnos</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>docentes</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
           <t>latitud</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>longitud</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>alumnos</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>docentes</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
